--- a/Planilha_Mestre_Panorama_v5.2.xlsx
+++ b/Planilha_Mestre_Panorama_v5.2.xlsx
@@ -1469,7 +1469,7 @@
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>Médio-alto</t>
+          <t>Médio</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
@@ -1492,10 +1492,10 @@
         <v>100.35</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>145.78</v>
+        <v>100.35</v>
       </c>
       <c r="M12" s="8" t="n">
-        <v>123.065</v>
+        <v>100.35</v>
       </c>
       <c r="N12" s="7" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>851000</v>
       </c>
       <c r="Q12" s="9" t="n">
-        <v>6850.038597489131</v>
+        <v>8400.597907324365</v>
       </c>
       <c r="R12" s="9" t="n"/>
       <c r="S12" s="10" t="n"/>
@@ -1531,12 +1531,12 @@
       <c r="W12" s="6" t="inlineStr"/>
       <c r="X12" s="6" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="Y12" s="7" t="inlineStr">
         <is>
-          <t>Condomínio horizontal (sobrados). Área casa 100,35 m² + terreno 136-146 m². ~38 casas. Lazer: campo society, piscina, deck, salão, gourmet, petplay, playground. Muitas unidades VENDIDAS. Entrega DEZ/2026. Ticket R$ 835-851k. R$/m² construção ~R$ 8.400. [reconstituído da v4.16 em 25/04/2026]</t>
+          <t>Condomínio horizontal (sobrados). 1 ÚNICA tipologia: casa 100,35 m² construída (área usada para R$/m²). Terreno varia 136-146 m² conforme posição. ~38 casas. Lazer: campo society, piscina, deck, salão, gourmet, petplay, playground. Muitas unidades VENDIDAS. Entrega 01/2029. Ticket R$ 835-851k → R$/m² construção ~R$ 8.400. CORREÇÃO v5.2: Área máx era 145,78 (terreno) — corrigida para 100,35 (construída). Convenção PADRAO §1: Tipo=Horizontal usa área construída.</t>
         </is>
       </c>
     </row>
@@ -3963,10 +3963,10 @@
         <v>154.64</v>
       </c>
       <c r="L37" s="14" t="n">
-        <v>180.98</v>
+        <v>154.64</v>
       </c>
       <c r="M37" s="14" t="n">
-        <v>167.81</v>
+        <v>154.64</v>
       </c>
       <c r="N37" s="13" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         <v>1415000</v>
       </c>
       <c r="Q37" s="15" t="n">
-        <v>8387.462010607234</v>
+        <v>9101.784790481119</v>
       </c>
       <c r="R37" s="15" t="n"/>
       <c r="S37" s="16" t="n"/>
@@ -4002,12 +4002,12 @@
       <c r="W37" s="12" t="inlineStr"/>
       <c r="X37" s="12" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="Y37" s="13" t="inlineStr">
         <is>
-          <t>Condomínio horizontal alto padrão. Casa 154,64 m² + terreno 170-181 m². Maioria das unidades VENDIDAS (14+ marcadas VENDIDA na tabela ABR/2026). Entrega JUL/2027. Ticket ~R$ 1,4M. R$/m² construção ~R$ 9.150. [reconstituído da v4.16 em 25/04/2026]</t>
+          <t>Condomínio horizontal alto padrão. 1 ÚNICA tipologia: casa 154,64 m² construída. Terreno varia 170-181 m² conforme posição. Maioria das unidades VENDIDAS (14+ marcadas VENDIDA na tabela ABR/2026). Entrega 06/2027. Ticket ~R$ 1,4M → R$/m² construção ~R$ 9.150. CORREÇÃO v5.2: Área máx era 180,98 (terreno) — corrigida para 154,64 (construída). Convenção PADRAO §1: Tipo=Horizontal usa área construída.</t>
         </is>
       </c>
     </row>
@@ -5984,7 +5984,7 @@
         <v>1052456.666666667</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>7301.887457600748</v>
+        <v>8056.848154170456</v>
       </c>
       <c r="K14" s="19" t="n">
         <v>0</v>
